--- a/artfynd/A 39923-2026 artfynd.xlsx
+++ b/artfynd/A 39923-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759859</v>
       </c>
       <c r="B2" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39923-2026 artfynd.xlsx
+++ b/artfynd/A 39923-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759859</v>
       </c>
       <c r="B2" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39923-2026 artfynd.xlsx
+++ b/artfynd/A 39923-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759859</v>
       </c>
       <c r="B2" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39923-2026 artfynd.xlsx
+++ b/artfynd/A 39923-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759859</v>
       </c>
       <c r="B2" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39923-2026 artfynd.xlsx
+++ b/artfynd/A 39923-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759859</v>
       </c>
       <c r="B2" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39923-2026 artfynd.xlsx
+++ b/artfynd/A 39923-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759859</v>
       </c>
       <c r="B2" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39923-2026 artfynd.xlsx
+++ b/artfynd/A 39923-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759859</v>
       </c>
       <c r="B2" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39923-2026 artfynd.xlsx
+++ b/artfynd/A 39923-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759859</v>
       </c>
       <c r="B2" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39923-2026 artfynd.xlsx
+++ b/artfynd/A 39923-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759859</v>
       </c>
       <c r="B2" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39923-2026 artfynd.xlsx
+++ b/artfynd/A 39923-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759859</v>
       </c>
       <c r="B2" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39923-2026 artfynd.xlsx
+++ b/artfynd/A 39923-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759859</v>
       </c>
       <c r="B2" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39923-2026 artfynd.xlsx
+++ b/artfynd/A 39923-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759859</v>
       </c>
       <c r="B2" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
